--- a/data/trans_orig/IP39B-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP39B-Edad-trans_orig.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5538</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>602</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6147</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2525</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5119</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9345</t>
+          <t>8762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8594</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20340</t>
+          <t>19768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,98%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46226</t>
+          <t>45454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56121</t>
+          <t>55902</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>50166</t>
+          <t>50374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>57561</t>
+          <t>58037</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>99588</t>
+          <t>99951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>112511</t>
+          <t>111787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4909</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4682</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6720</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5408</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>7988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6572</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>18065</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>32871</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15224</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>29076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37140</t>
+          <t>36541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57007</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>105458</t>
+          <t>104744</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120110</t>
+          <t>120465</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107007</t>
+          <t>107209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>121632</t>
+          <t>121371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>216954</t>
+          <t>217289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238600</t>
+          <t>239183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,49%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2989</t>
+          <t>3576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3555</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>616</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1319</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>6891</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10853</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,87%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>712</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7176</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2758</t>
+          <t>2653</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4619</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13081</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4827</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23105</t>
+          <t>23543</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>35933</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>45705</t>
+          <t>46240</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60408</t>
+          <t>60406</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71621</t>
+          <t>72128</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101010</t>
+          <t>100675</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>115486</t>
+          <t>115996</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4429</t>
+          <t>4702</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>636</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>538</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3643</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>686</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6635</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,2%</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8544</t>
+          <t>8475</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>9099</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>5258</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21967</t>
+          <t>21748</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14544</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27900</t>
+          <t>27312</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27156</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45189</t>
+          <t>46283</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77339</t>
+          <t>77820</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>91584</t>
+          <t>91872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,42%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>71021</t>
+          <t>71083</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>85387</t>
+          <t>85178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152617</t>
+          <t>153202</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>173771</t>
+          <t>173483</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,4%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,16%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>24799</t>
+          <t>25943</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>47013</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>71620</t>
+          <t>70260</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>45515</t>
+          <t>44917</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>67526</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>96963</t>
+          <t>97791</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>129354</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>278715</t>
+          <t>278170</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>303646</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>303552</t>
+          <t>302472</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>326633</t>
+          <t>327219</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>589580</t>
+          <t>588313</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>624468</t>
+          <t>623294</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4174</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>6159</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5082</t>
+          <t>5614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>9845</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2645</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>9611</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2529</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>10151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6792</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17029</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47477</t>
+          <t>47384</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56889</t>
+          <t>56642</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>47451</t>
+          <t>47707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56798</t>
+          <t>56888</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97632</t>
+          <t>97775</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>110938</t>
+          <t>111488</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,53%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4296</t>
+          <t>4382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1462</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8349</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>9476</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6850</t>
+          <t>6258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10042</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>22173</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24390</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23749</t>
+          <t>23740</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40984</t>
+          <t>41241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,21%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>72259</t>
+          <t>71938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>86739</t>
+          <t>86391</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>93658</t>
+          <t>93957</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108115</t>
+          <t>108161</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>170850</t>
+          <t>170894</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190501</t>
+          <t>191050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4150</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2706</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5984,7 +5984,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>673</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>1865</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8807</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4838</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4505</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23920</t>
+          <t>23950</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>55940</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66124</t>
+          <t>66119</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59001</t>
+          <t>58242</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69471</t>
+          <t>69032</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117933</t>
+          <t>118893</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133140</t>
+          <t>133222</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,59%</t>
         </is>
       </c>
     </row>
@@ -6425,7 +6425,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1235</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7137</t>
+          <t>7077</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7840</t>
+          <t>8094</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6573,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4098</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4537</t>
+          <t>4057</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>574</t>
+          <t>580</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1165</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>6425</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16400</t>
+          <t>16259</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5926</t>
+          <t>5867</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15576</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14388</t>
+          <t>14286</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28550</t>
+          <t>27860</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>60564</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>71349</t>
+          <t>71531</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>48408</t>
+          <t>48774</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>60258</t>
+          <t>60574</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,8%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>113646</t>
+          <t>113241</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>128857</t>
+          <t>128982</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>28138</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>50564</t>
+          <t>50300</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31409</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>50792</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>67237</t>
+          <t>67471</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>94888</t>
+          <t>95253</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>249229</t>
+          <t>248741</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>271182</t>
+          <t>271594</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>262098</t>
+          <t>262097</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>284226</t>
+          <t>285319</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>517267</t>
+          <t>518936</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>551568</t>
+          <t>551817</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>678</t>
+          <t>718</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6163</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4407</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>3970</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>6185</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>606</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>6592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>533</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5064</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1670</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10255</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1848</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6122</t>
+          <t>6062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16143</t>
+          <t>15822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>43510</t>
+          <t>43314</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52960</t>
+          <t>53293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49713</t>
+          <t>50239</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>58679</t>
+          <t>58774</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,11%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>95791</t>
+          <t>97040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>109918</t>
+          <t>109681</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>88,92%</t>
         </is>
       </c>
     </row>
@@ -8703,7 +8703,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3708</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2738</t>
+          <t>2764</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8773,7 +8773,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>3988</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>493</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>563</t>
+          <t>565</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>5353</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>6787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9374</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6711</t>
+          <t>7193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16973</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8029</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>19264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17389</t>
+          <t>17028</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32044</t>
+          <t>31156</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,16%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85336</t>
+          <t>85544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>97219</t>
+          <t>96910</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106515</t>
+          <t>105775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>118622</t>
+          <t>117674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195720</t>
+          <t>195599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212265</t>
+          <t>212762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5714</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>6184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>3791</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5378</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9548,7 +9548,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -9611,7 +9611,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3705</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>738</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6732</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8139</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7949</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18882</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1429</t>
+          <t>1794</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>8169</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11234</t>
+          <t>11008</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24182</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,61%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70890</t>
+          <t>70811</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82021</t>
+          <t>81966</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76192</t>
+          <t>75245</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86382</t>
+          <t>85533</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>150421</t>
+          <t>150088</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>165086</t>
+          <t>165163</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -10067,7 +10067,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10082,7 +10082,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3581</t>
+          <t>3167</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10215,7 +10215,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3511</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4262</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10265,7 +10265,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -10293,7 +10293,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4479</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1401</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2125</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,11%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3937</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>12607</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>25498</t>
+          <t>25716</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61999</t>
+          <t>62998</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>72425</t>
+          <t>72705</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>65153</t>
+          <t>64999</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>76989</t>
+          <t>76971</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>130967</t>
+          <t>131915</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>147299</t>
+          <t>147357</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18366</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46760</t>
+          <t>46838</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>40474</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>57332</t>
+          <t>58119</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>84493</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>276656</t>
+          <t>274531</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>295781</t>
+          <t>295688</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>309397</t>
+          <t>308410</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>329914</t>
+          <t>331188</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>590035</t>
+          <t>588387</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>620637</t>
+          <t>620559</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,12 +11281,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
